--- a/artfynd/A 42054-2022 artfynd.xlsx
+++ b/artfynd/A 42054-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132154779</v>
       </c>
       <c r="B2" t="n">
-        <v>91934</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>132154802</v>
       </c>
       <c r="B3" t="n">
-        <v>91934</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>132154818</v>
       </c>
       <c r="B4" t="n">
-        <v>91934</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,6 +976,214 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132155217</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nybygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>553946</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6468210</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132154822</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nybygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>553891</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6468216</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bankekind</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42054-2022 artfynd.xlsx
+++ b/artfynd/A 42054-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132154779</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132154802</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132154818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132155217</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,8 +1208,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132154822</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>